--- a/1toolConverter_local/tablas_extraidas.xlsx
+++ b/1toolConverter_local/tablas_extraidas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -591,12 +591,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Probe_1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Probe 1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -607,7 +607,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -635,11 +635,7 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -695,12 +691,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Probe_2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Probe 2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -711,7 +707,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -739,11 +735,7 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -799,12 +791,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Probe_3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Probe 3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -815,7 +807,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -843,11 +835,7 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -903,12 +891,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Probe_4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Probe 4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -919,7 +907,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -947,11 +935,7 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -1007,12 +991,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Regulation_probe</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Regulation probe</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1023,7 +1007,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1051,11 +1035,7 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -1111,12 +1091,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Real-time_speed_VSC1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Real-time speed VSC1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1127,7 +1107,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1155,11 +1135,7 @@
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -1215,12 +1191,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Real-time_speed_VSC2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Real-time speed VSC2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1231,7 +1207,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1259,11 +1235,7 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -1319,12 +1291,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>SetPoint_VSC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>SetPoint VSC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1363,11 +1335,7 @@
       <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -1423,12 +1391,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>SetPoint_On/Off</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>SetPoint On/Off</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1467,11 +1435,7 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>16bit</t>
@@ -1527,12 +1491,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Digital_input_1_status</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Digital input 1 status</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1571,11 +1535,7 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -1631,12 +1591,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Digital_input_2_status</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Digital input 2 status</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1675,11 +1635,7 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -1735,12 +1691,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>ONOFF_output_status</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>ONOFF output status</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1751,7 +1707,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1779,11 +1735,7 @@
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -1839,12 +1791,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Defrost_1_output_status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Defrost 1 output status</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1855,7 +1807,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1883,11 +1835,7 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -1943,12 +1891,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Defrost_2_output_status</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Defrost 2 output status</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1959,7 +1907,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1987,11 +1935,7 @@
       <c r="P15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2047,12 +1991,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Alarm_output_status</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Alarm output status</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2063,7 +2007,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2091,11 +2035,7 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2151,12 +2091,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Light_output_status</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Light output status</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2167,7 +2107,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2195,11 +2135,7 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2255,12 +2191,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Fan_output_status</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Fan output status</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2271,7 +2207,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2299,11 +2235,7 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2359,12 +2291,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Aux_output_status</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Aux output status</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2375,7 +2307,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2403,11 +2335,7 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2463,12 +2391,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Dead_band_output_status</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Dead band output status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2479,7 +2407,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2507,11 +2435,7 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2567,12 +2491,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Compressor_1_output_status</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Compressor 1 output status</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2583,7 +2507,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2611,11 +2535,7 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2671,12 +2591,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Compressor_2_output_status</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Compressor 2 output status</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2687,7 +2607,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2715,11 +2635,7 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2775,12 +2691,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Buzzer_status</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Buzzer status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2791,7 +2707,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2819,11 +2735,7 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2879,12 +2791,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Condenser_fan_output_status</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Condenser fan output status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2895,7 +2807,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2923,11 +2835,7 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -2983,12 +2891,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Heaters_output_status</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Heaters output status</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2999,7 +2907,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3027,11 +2935,7 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3087,12 +2991,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Device_ON</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Device ON</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3131,11 +3035,7 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3191,12 +3091,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>Defrost_status</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Defrost status</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3235,11 +3135,7 @@
       <c r="P27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3295,12 +3191,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>Pull_down_status</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Pull down status</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3339,11 +3235,7 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3399,12 +3291,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>Keyboard_lock/unlock</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Keyboard lock/unlock</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3443,11 +3335,7 @@
       <c r="P29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3503,12 +3391,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>Alarm_muting</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>Alarm muting</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3547,11 +3435,7 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3607,12 +3491,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Energy_saving_status</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Energy saving status</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3651,11 +3535,7 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3711,12 +3591,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Holiday_status</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Holiday status</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3755,11 +3635,7 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3815,12 +3691,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>Test_mode_set_point_used</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Test mode set point used</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3859,11 +3735,7 @@
       <c r="P33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3919,12 +3791,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Probe_1_error</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>Probe 1 error</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3963,11 +3835,7 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -3976,7 +3844,7 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4023,12 +3891,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Probe_2_error</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>Probe 2 error</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4067,11 +3935,7 @@
       <c r="P35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4080,7 +3944,7 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4127,12 +3991,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Probe_3_error</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>Probe 3 error</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4171,11 +4035,7 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4184,7 +4044,7 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4231,12 +4091,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Probe_4_error</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Probe 4 error</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4275,11 +4135,7 @@
       <c r="P37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4288,7 +4144,7 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4335,12 +4191,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Hight_temperature_alarm</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>Hight temperature alarm</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4379,11 +4235,7 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4392,7 +4244,7 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4439,12 +4291,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Low_temperature_alarm</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Low temperature alarm</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4483,11 +4335,7 @@
       <c r="P39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4496,7 +4344,7 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4543,12 +4391,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Condenser_high_temperature_alarm</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>Condenser high temperature alarm</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4587,11 +4435,7 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4600,7 +4444,7 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4647,12 +4491,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Condenser_low_temperature_alarm</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>Condenser low temperature alarm</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4691,11 +4535,7 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4704,7 +4544,7 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4751,12 +4591,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>External_warning_Alarm</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>External warning Alarm</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4795,11 +4635,7 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4808,7 +4644,7 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4855,12 +4691,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Lock_alarm</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Lock alarm</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4899,11 +4735,7 @@
       <c r="P43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -4912,7 +4744,7 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4959,12 +4791,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Door_open_alarm</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>Door open alarm</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5003,11 +4835,7 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -5016,7 +4844,7 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5063,12 +4891,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>EEPROM_failure</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>EEPROM failure</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5107,11 +4935,7 @@
       <c r="P45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -5120,7 +4944,7 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5167,12 +4991,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Pressure_switch_alarm</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>Pressure switch alarm</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5211,11 +5035,7 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -5224,7 +5044,7 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5271,12 +5091,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Real_time_clock_configuration_error</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>Real time clock configuration error</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5315,11 +5135,7 @@
       <c r="P47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -5328,7 +5144,7 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5375,12 +5191,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Embraco_compressor_Error</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>Embraco compressor Error</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5419,11 +5235,7 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -5432,7 +5244,7 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5479,12 +5291,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>Secop_compressor_Error</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>Secop compressor Error</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5523,11 +5335,7 @@
       <c r="P49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -5536,7 +5344,7 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5583,12 +5391,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Compressor_1:_comunication_alarm</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Compressor 1: comunication alarm</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5627,11 +5435,7 @@
       <c r="P50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -5640,7 +5444,7 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5687,12 +5491,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Compressor_2:_comunication_alarm</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>Compressor 2: comunication alarm</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5731,11 +5535,7 @@
       <c r="P51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -5744,7 +5544,7 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>{"severity":"none"}</t>
+          <t>{"severity":"high"}</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5791,12 +5591,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Device ON_1</t>
+          <t>Device_ON_1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Device ON</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5817,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -5837,7 +5637,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5895,12 +5695,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Device_OFF</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>Device OFF</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5921,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -5999,12 +5799,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>Defrost_ON</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Defrost ON</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6025,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -6045,7 +5845,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6103,12 +5903,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Pull_Down_ON</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>Pull Down ON</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6129,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -6149,7 +5949,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -6207,12 +6007,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>Pull_Down_OFF</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>Pull Down OFF</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6233,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -6311,12 +6111,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alarm Muting_1</t>
+          <t>Alarm_Muting_1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Alarm Muting</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6337,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -6357,7 +6157,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6415,12 +6215,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Energy_saving_ON</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>Energy saving ON</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6441,7 +6241,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -6461,7 +6261,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -6519,12 +6319,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>Energy_saving_OFF</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>Energy saving OFF</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6545,7 +6345,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -6623,12 +6423,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Light_ON</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>Light ON</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6649,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -6669,7 +6469,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6727,12 +6527,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>Light_OFF</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>Light OFF</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6753,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -6831,12 +6631,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Aux_ON</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>Aux ON</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6857,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -6877,7 +6677,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6935,12 +6735,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Aux_OFF</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>Aux OFF</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6961,7 +6761,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -7039,12 +6839,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Holiday_ON</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>Holiday ON</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7065,7 +6865,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -7085,7 +6885,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -7143,12 +6943,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>Holiday_OFF</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>Holiday OFF</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Add</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7169,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -7295,11 +7095,7 @@
       <c r="P66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>s16</t>
@@ -7403,11 +7199,7 @@
       <c r="P67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
           <t>s16</t>
@@ -7511,11 +7303,7 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
           <t>s16</t>
@@ -7627,11 +7415,7 @@
       <c r="P69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
           <t>s16</t>
@@ -7743,11 +7527,7 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
           <t>u8</t>
@@ -7859,11 +7639,7 @@
       <c r="P71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
           <t>u8</t>
@@ -7975,11 +7751,7 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
           <t>s16</t>
@@ -8091,11 +7863,7 @@
       <c r="P73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
           <t>s16</t>
@@ -8156,7 +7924,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Activation mode for 2nd compressor: HAFstep logic; FULdela</t>
+          <t>Activation mode for 2nd compressor: HAFstep logic; FULdelayed</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8199,11 +7967,7 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -8307,11 +8071,7 @@
       <c r="P75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -8423,11 +8183,7 @@
       <c r="P76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
           <t>u8</t>
@@ -8531,11 +8287,7 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>2bit</t>
@@ -8643,11 +8395,7 @@
       <c r="P78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
           <t>u8</t>
@@ -8759,11 +8507,7 @@
       <c r="P79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
           <t>s16</t>
@@ -8875,11 +8619,7 @@
       <c r="P80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
           <t>u8</t>
@@ -8940,7 +8680,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Threshold for automatic activation of Pull Down in normal mo</t>
+          <t>Threshold for automatic activation of Pull Down in normal mode SETHYoHt</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8991,11 +8731,7 @@
       <c r="P81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
           <t>u8</t>
@@ -9107,11 +8843,7 @@
       <c r="P82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
           <t>u8</t>
@@ -9223,11 +8955,7 @@
       <c r="P83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
           <t>u8</t>
@@ -9339,11 +9067,7 @@
       <c r="P84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>u8</t>
@@ -9404,7 +9128,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Delay before activation of the second compressor when T SE</t>
+          <t>Delay before activation of the second compressor when T SETHYHY1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9455,11 +9179,7 @@
       <c r="P85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
           <t>u8</t>
@@ -9520,7 +9240,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Delay before deactivation of the second compressor after any</t>
+          <t>Delay before deactivation of the second compressor after any pull down</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9571,11 +9291,7 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
           <t>u8</t>
@@ -9687,11 +9403,7 @@
       <c r="P87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
           <t>u8</t>
@@ -9803,11 +9515,7 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>u8</t>
@@ -9911,11 +9619,7 @@
       <c r="P89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -10027,11 +9731,7 @@
       <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
           <t>u8</t>
@@ -10135,11 +9835,7 @@
       <c r="P91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -10251,11 +9947,7 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
           <t>u8</t>
@@ -10359,11 +10051,7 @@
       <c r="P93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -10475,11 +10163,7 @@
       <c r="P94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
           <t>u8</t>
@@ -10583,11 +10267,7 @@
       <c r="P95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -10699,11 +10379,7 @@
       <c r="P96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
           <t>u8</t>
@@ -10815,11 +10491,7 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
           <t>u8</t>
@@ -10931,11 +10603,7 @@
       <c r="P98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
           <t>u8</t>
@@ -11047,11 +10715,7 @@
       <c r="P99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
           <t>u8</t>
@@ -11155,11 +10819,7 @@
       <c r="P100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
           <t>s16</t>
@@ -11263,11 +10923,7 @@
       <c r="P101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
           <t>s16</t>
@@ -11375,11 +11031,7 @@
       <c r="P102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
           <t>s16</t>
@@ -11491,11 +11143,7 @@
       <c r="P103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
           <t>u8</t>
@@ -11607,11 +11255,7 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
           <t>u8</t>
@@ -11715,11 +11359,7 @@
       <c r="P105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -11780,7 +11420,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Signal output variation for Variable Speed Compressor SET-H</t>
+          <t>Signal output variation for Variable Speed Compressor SET-HYTSETHY</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -11827,11 +11467,7 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
           <t>s16</t>
@@ -11892,7 +11528,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Signal output variation for Variable Speed Compressor SET-H</t>
+          <t>Signal output variation for Variable Speed Compressor SET-HY-HYSTSET- HY e SETHYTSETHYPb</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11939,11 +11575,7 @@
       <c r="P107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
           <t>s16</t>
@@ -12004,7 +11636,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Signal output variation for Variable Speed Compressor TSET</t>
+          <t>Signal output variation for Variable Speed Compressor TSET-HY-HY1 e TSETHYPb</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -12051,11 +11683,7 @@
       <c r="P108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
           <t>s16</t>
@@ -12116,7 +11744,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Variable Speed Compressor in percentage during any Pull Do</t>
+          <t>Variable Speed Compressor in percentage during any Pull Down</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -12167,11 +11795,7 @@
       <c r="P109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
           <t>u8</t>
@@ -12232,7 +11856,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Compressor speed in % in case of any probe error during Co</t>
+          <t>Compressor speed in % in case of any probe error during Con interval</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -12283,11 +11907,7 @@
       <c r="P110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
           <t>u8</t>
@@ -12348,7 +11968,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Compressor speed in % during any defrost cycle valid if t</t>
+          <t>Compressor speed in % during any defrost cycle valid if tdfin</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -12399,11 +12019,7 @@
       <c r="P111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
           <t>u8</t>
@@ -12464,7 +12080,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Compressor speed during any pre-defrost phase valid if tdf</t>
+          <t>Compressor speed during any pre-defrost phase valid if tdfin</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -12515,11 +12131,7 @@
       <c r="P112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
           <t>u8</t>
@@ -12623,11 +12235,7 @@
       <c r="P113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
           <t>u8</t>
@@ -12731,11 +12339,7 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
           <t>u8</t>
@@ -12843,11 +12447,7 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
           <t>u8</t>
@@ -12959,11 +12559,7 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
           <t>u8</t>
@@ -13024,7 +12620,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PI regulator: divisor for PI response time reduction acts o</t>
+          <t>PI regulator: divisor for PI response time reduction acts on both par. tSt and iSt</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -13071,11 +12667,7 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -13179,11 +12771,7 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -13287,11 +12875,7 @@
       <c r="P119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -13352,7 +12936,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Compressor speed threshold to activate lubrication valid on</t>
+          <t>Compressor speed threshold to activate lubrication valid only for variable speed compressors, 0disabled</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -13399,11 +12983,7 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
           <t>u8</t>
@@ -13464,7 +13044,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Time range with compressor speed below MnP to activate lubri</t>
+          <t>Time range with compressor speed below MnP to activate lubrication cycle</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -13515,11 +13095,7 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
           <t>u8</t>
@@ -13580,7 +13156,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Time range with compressor speed at 100% to activate lubrica</t>
+          <t>Time range with compressor speed at 100% to activate lubrication cycle</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -13631,11 +13207,7 @@
       <c r="P122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
           <t>u8</t>
@@ -13743,11 +13315,7 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -13855,11 +13423,7 @@
       <c r="P124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
           <t>u8</t>
@@ -13967,11 +13531,7 @@
       <c r="P125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr">
         <is>
           <t>u8</t>
@@ -14075,11 +13635,7 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -14183,11 +13739,7 @@
       <c r="P127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -14291,11 +13843,7 @@
       <c r="P128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -14407,11 +13955,7 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr">
         <is>
           <t>u8</t>
@@ -14472,7 +14016,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Probe visualization percentageFP1;P2 ex: dtr1 means VAL</t>
+          <t>Probe visualization percentageFP1;P2 ex: dtr1 means VALUE0.01P10.99P2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -14519,11 +14063,7 @@
       <c r="P130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
           <t>u8</t>
@@ -14627,11 +14167,7 @@
       <c r="P131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
           <t>2bit</t>
@@ -14735,11 +14271,7 @@
       <c r="P132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -14843,11 +14375,7 @@
       <c r="P133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -14951,11 +14479,7 @@
       <c r="P134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -15067,11 +14591,7 @@
       <c r="P135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr">
         <is>
           <t>s16</t>
@@ -15183,11 +14703,7 @@
       <c r="P136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr">
         <is>
           <t>s16</t>
@@ -15299,11 +14815,7 @@
       <c r="P137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr">
         <is>
           <t>u8</t>
@@ -15415,11 +14927,7 @@
       <c r="P138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
         <is>
           <t>u8</t>
@@ -15531,11 +15039,7 @@
       <c r="P139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
           <t>u8</t>
@@ -15647,11 +15151,7 @@
       <c r="P140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
           <t>u8</t>
@@ -15763,11 +15263,7 @@
       <c r="P141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr">
         <is>
           <t>u8</t>
@@ -15871,11 +15367,7 @@
       <c r="P142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -15987,11 +15479,7 @@
       <c r="P143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr">
         <is>
           <t>u8</t>
@@ -16103,11 +15591,7 @@
       <c r="P144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr">
         <is>
           <t>u8</t>
@@ -16219,11 +15703,7 @@
       <c r="P145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr">
         <is>
           <t>u8</t>
@@ -16284,7 +15764,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sampling time to calculate the average compressor speed befo</t>
+          <t>Sampling time to calculate the average compressor speed before any desfrost cycle</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -16335,11 +15815,7 @@
       <c r="P146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr">
         <is>
           <t>u8</t>
@@ -16443,11 +15919,7 @@
       <c r="P147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -16559,11 +16031,7 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr">
         <is>
           <t>u8</t>
@@ -16667,11 +16135,7 @@
       <c r="P149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -16779,11 +16243,7 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr">
         <is>
           <t>u8</t>
@@ -16887,11 +16347,7 @@
       <c r="P151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -17003,11 +16459,7 @@
       <c r="P152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
           <t>s16</t>
@@ -17119,11 +16571,7 @@
       <c r="P153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr">
         <is>
           <t>u8</t>
@@ -17227,11 +16675,7 @@
       <c r="P154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr">
         <is>
           <t>2bit</t>
@@ -17343,11 +16787,7 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr">
         <is>
           <t>u8</t>
@@ -17408,7 +16848,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Differential temperature for cyclic activation of evaporator</t>
+          <t>Differential temperature for cyclic activation of evaporator fans 0disabled</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -17459,11 +16899,7 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr">
         <is>
           <t>u8</t>
@@ -17567,11 +17003,7 @@
       <c r="P157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -17683,11 +17115,7 @@
       <c r="P158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -17799,11 +17227,7 @@
       <c r="P159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -17911,11 +17335,7 @@
       <c r="P160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr">
         <is>
           <t>s16</t>
@@ -18019,11 +17439,7 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -18127,11 +17543,7 @@
       <c r="P162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -18243,11 +17655,7 @@
       <c r="P163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr">
         <is>
           <t>s16</t>
@@ -18359,11 +17767,7 @@
       <c r="P164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr">
         <is>
           <t>u8</t>
@@ -18467,11 +17871,7 @@
       <c r="P165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -18583,11 +17983,7 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr">
         <is>
           <t>s16</t>
@@ -18695,11 +18091,7 @@
       <c r="P167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr">
         <is>
           <t>s16</t>
@@ -18803,11 +18195,7 @@
       <c r="P168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -18868,7 +18256,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Number of Group 1 serial condenser fans 0 Group 1 disable</t>
+          <t>Number of Group 1 serial condenser fans 0 Group 1 disabled</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -18915,11 +18303,7 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -19027,11 +18411,7 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr">
         <is>
           <t>u8</t>
@@ -19139,11 +18519,7 @@
       <c r="P171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr">
         <is>
           <t>u8</t>
@@ -19204,7 +18580,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Number of Group 2 serial condenser fans 0 Group 2 disable</t>
+          <t>Number of Group 2 serial condenser fans 0 Group 2 disabled</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -19251,11 +18627,7 @@
       <c r="P172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -19363,11 +18735,7 @@
       <c r="P173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr">
         <is>
           <t>u8</t>
@@ -19475,11 +18843,7 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr">
         <is>
           <t>u8</t>
@@ -19583,11 +18947,7 @@
       <c r="P175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -19695,11 +19055,7 @@
       <c r="P176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr">
         <is>
           <t>s16</t>
@@ -19803,11 +19159,7 @@
       <c r="P177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -19911,11 +19263,7 @@
       <c r="P178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr">
         <is>
           <t>s16</t>
@@ -20019,11 +19367,7 @@
       <c r="P179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr">
         <is>
           <t>s16</t>
@@ -20127,11 +19471,7 @@
       <c r="P180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr">
         <is>
           <t>s16</t>
@@ -20235,11 +19575,7 @@
       <c r="P181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr">
         <is>
           <t>2bit</t>
@@ -20343,11 +19679,7 @@
       <c r="P182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -20455,11 +19787,7 @@
       <c r="P183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr">
         <is>
           <t>s16</t>
@@ -20567,11 +19895,7 @@
       <c r="P184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr">
         <is>
           <t>u8</t>
@@ -20675,11 +19999,7 @@
       <c r="P185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -20787,11 +20107,7 @@
       <c r="P186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr">
         <is>
           <t>s16</t>
@@ -20895,11 +20211,7 @@
       <c r="P187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr">
         <is>
           <t>s16</t>
@@ -21003,11 +20315,7 @@
       <c r="P188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr">
         <is>
           <t>s16</t>
@@ -21111,11 +20419,7 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr">
         <is>
           <t>s16</t>
@@ -21219,11 +20523,7 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr">
         <is>
           <t>2bit</t>
@@ -21327,11 +20627,7 @@
       <c r="P191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -21439,11 +20735,7 @@
       <c r="P192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr">
         <is>
           <t>s16</t>
@@ -21551,11 +20843,7 @@
       <c r="P193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr">
         <is>
           <t>u8</t>
@@ -21659,11 +20947,7 @@
       <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -21771,11 +21055,7 @@
       <c r="P195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
           <t>s16</t>
@@ -21879,11 +21159,7 @@
       <c r="P196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -21995,11 +21271,7 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr">
         <is>
           <t>s16</t>
@@ -22111,11 +21383,7 @@
       <c r="P198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr">
         <is>
           <t>u8</t>
@@ -22219,11 +21487,7 @@
       <c r="P199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -22327,11 +21591,7 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -22435,11 +21695,7 @@
       <c r="P201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -22551,11 +21807,7 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr">
         <is>
           <t>u8</t>
@@ -22667,11 +21919,7 @@
       <c r="P203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr">
         <is>
           <t>u8</t>
@@ -22775,11 +22023,7 @@
       <c r="P204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -22883,11 +22127,7 @@
       <c r="P205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -22999,11 +22239,7 @@
       <c r="P206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr">
         <is>
           <t>s16</t>
@@ -23115,11 +22351,7 @@
       <c r="P207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
         <is>
           <t>s16</t>
@@ -23231,11 +22463,7 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr">
         <is>
           <t>u8</t>
@@ -23347,11 +22575,7 @@
       <c r="P209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr">
         <is>
           <t>u8</t>
@@ -23463,11 +22687,7 @@
       <c r="P210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr">
         <is>
           <t>u8</t>
@@ -23579,11 +22799,7 @@
       <c r="P211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
           <t>u8</t>
@@ -23687,11 +22903,7 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -23803,11 +23015,7 @@
       <c r="P213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr">
         <is>
           <t>s16</t>
@@ -23919,11 +23127,7 @@
       <c r="P214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr">
         <is>
           <t>s16</t>
@@ -24035,11 +23239,7 @@
       <c r="P215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr">
         <is>
           <t>u8</t>
@@ -24151,11 +23351,7 @@
       <c r="P216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
           <t>u8</t>
@@ -24267,11 +23463,7 @@
       <c r="P217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr">
         <is>
           <t>u8</t>
@@ -24375,11 +23567,7 @@
       <c r="P218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -24483,11 +23671,7 @@
       <c r="P219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -24599,11 +23783,7 @@
       <c r="P220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr">
         <is>
           <t>u8</t>
@@ -24707,11 +23887,7 @@
       <c r="P221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -24815,11 +23991,7 @@
       <c r="P222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -24923,11 +24095,7 @@
       <c r="P223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr">
         <is>
           <t>u8</t>
@@ -25031,11 +24199,7 @@
       <c r="P224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr">
         <is>
           <t>u8</t>
@@ -25139,11 +24303,7 @@
       <c r="P225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr">
         <is>
           <t>u8</t>
@@ -25247,11 +24407,7 @@
       <c r="P226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
         <is>
           <t>u8</t>
@@ -25355,11 +24511,7 @@
       <c r="P227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr">
         <is>
           <t>u8</t>
@@ -25463,11 +24615,7 @@
       <c r="P228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -25571,11 +24719,7 @@
       <c r="P229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -25679,11 +24823,7 @@
       <c r="P230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -25787,11 +24927,7 @@
       <c r="P231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -25903,11 +25039,7 @@
       <c r="P232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr">
         <is>
           <t>u8</t>
@@ -26011,11 +25143,7 @@
       <c r="P233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -26119,11 +25247,7 @@
       <c r="P234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -26235,11 +25359,7 @@
       <c r="P235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr">
         <is>
           <t>u8</t>
@@ -26300,7 +25420,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Number of external pressure switch alarms before stopping th</t>
+          <t>Number of external pressure switch alarms before stopping the regulation</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -26347,11 +25467,7 @@
       <c r="P236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -26455,11 +25571,7 @@
       <c r="P237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr">
         <is>
           <t>2bit</t>
@@ -26563,11 +25675,7 @@
       <c r="P238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -26679,11 +25787,7 @@
       <c r="P239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr">
         <is>
           <t>s16</t>
@@ -26744,7 +25848,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Energy saving controls the lights lights OFF when energy sa</t>
+          <t>Energy saving controls the lights lights OFF when energy saving goes active</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -26787,11 +25891,7 @@
       <c r="P240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -26899,11 +25999,7 @@
       <c r="P241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -27011,11 +26107,7 @@
       <c r="P242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -27119,11 +26211,7 @@
       <c r="P243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -27231,11 +26319,7 @@
       <c r="P244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -27343,11 +26427,7 @@
       <c r="P245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -27455,11 +26535,7 @@
       <c r="P246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -27563,11 +26639,7 @@
       <c r="P247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -27671,11 +26743,7 @@
       <c r="P248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -27787,11 +26855,7 @@
       <c r="P249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr">
         <is>
           <t>u8</t>
@@ -27903,11 +26967,7 @@
       <c r="P250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr">
         <is>
           <t>u8</t>
@@ -28019,11 +27079,7 @@
       <c r="P251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr">
         <is>
           <t>u8</t>
@@ -28135,11 +27191,7 @@
       <c r="P252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr">
         <is>
           <t>u8</t>
@@ -28243,11 +27295,7 @@
       <c r="P253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q253" t="inlineStr"/>
       <c r="R253" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -28351,11 +27399,7 @@
       <c r="P254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -28459,11 +27503,7 @@
       <c r="P255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -28567,11 +27607,7 @@
       <c r="P256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -28675,11 +27711,7 @@
       <c r="P257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -28783,11 +27815,7 @@
       <c r="P258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -28891,11 +27919,7 @@
       <c r="P259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q259" t="inlineStr"/>
       <c r="R259" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -29007,11 +28031,7 @@
       <c r="P260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr">
         <is>
           <t>u8</t>
@@ -29123,11 +28143,7 @@
       <c r="P261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr">
         <is>
           <t>u8</t>
@@ -29239,11 +28255,7 @@
       <c r="P262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr">
         <is>
           <t>u8</t>
@@ -29355,11 +28367,7 @@
       <c r="P263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q263" t="inlineStr"/>
       <c r="R263" t="inlineStr">
         <is>
           <t>u8</t>
@@ -29471,11 +28479,7 @@
       <c r="P264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q264" t="inlineStr"/>
       <c r="R264" t="inlineStr">
         <is>
           <t>u8</t>
@@ -29587,11 +28591,7 @@
       <c r="P265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q265" t="inlineStr"/>
       <c r="R265" t="inlineStr">
         <is>
           <t>u8</t>
@@ -29699,11 +28699,7 @@
       <c r="P266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q266" t="inlineStr"/>
       <c r="R266" t="inlineStr">
         <is>
           <t>u8</t>
@@ -29807,11 +28803,7 @@
       <c r="P267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q267" t="inlineStr"/>
       <c r="R267" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -29915,11 +28907,7 @@
       <c r="P268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q268" t="inlineStr"/>
       <c r="R268" t="inlineStr">
         <is>
           <t>2bit</t>
@@ -30031,11 +29019,7 @@
       <c r="P269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q269" t="inlineStr"/>
       <c r="R269" t="inlineStr">
         <is>
           <t>u8</t>
@@ -30139,11 +29123,7 @@
       <c r="P270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q270" t="inlineStr"/>
       <c r="R270" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -30247,11 +29227,7 @@
       <c r="P271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q271" t="inlineStr"/>
       <c r="R271" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -30355,11 +29331,7 @@
       <c r="P272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q272" t="inlineStr"/>
       <c r="R272" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -30463,11 +29435,7 @@
       <c r="P273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q273" t="inlineStr"/>
       <c r="R273" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -30571,11 +29539,7 @@
       <c r="P274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q274" t="inlineStr"/>
       <c r="R274" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -30679,11 +29643,7 @@
       <c r="P275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q275" t="inlineStr"/>
       <c r="R275" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -30787,11 +29747,7 @@
       <c r="P276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q276" t="inlineStr"/>
       <c r="R276" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -30895,11 +29851,7 @@
       <c r="P277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -31003,11 +29955,7 @@
       <c r="P278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q278" t="inlineStr"/>
       <c r="R278" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -31111,11 +30059,7 @@
       <c r="P279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q279" t="inlineStr"/>
       <c r="R279" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -31219,11 +30163,7 @@
       <c r="P280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q280" t="inlineStr"/>
       <c r="R280" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -31327,11 +30267,7 @@
       <c r="P281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q281" t="inlineStr"/>
       <c r="R281" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -31435,11 +30371,7 @@
       <c r="P282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q282" t="inlineStr"/>
       <c r="R282" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -31543,11 +30475,7 @@
       <c r="P283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q283" t="inlineStr"/>
       <c r="R283" t="inlineStr">
         <is>
           <t>4bit</t>
@@ -31651,11 +30579,7 @@
       <c r="P284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q284" t="inlineStr"/>
       <c r="R284" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -31759,11 +30683,7 @@
       <c r="P285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q285" t="inlineStr"/>
       <c r="R285" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -31867,11 +30787,7 @@
       <c r="P286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q286" t="inlineStr"/>
       <c r="R286" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -31975,11 +30891,7 @@
       <c r="P287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q287" t="inlineStr"/>
       <c r="R287" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -32083,11 +30995,7 @@
       <c r="P288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -32191,11 +31099,7 @@
       <c r="P289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -32299,11 +31203,7 @@
       <c r="P290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q290" t="inlineStr"/>
       <c r="R290" t="inlineStr">
         <is>
           <t>1bit</t>
@@ -32407,11 +31307,7 @@
       <c r="P291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q291" t="inlineStr"/>
       <c r="R291" t="inlineStr">
         <is>
           <t>s16</t>
@@ -32515,11 +31411,7 @@
       <c r="P292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="Q292" t="inlineStr"/>
       <c r="R292" t="inlineStr">
         <is>
           <t>s16</t>

--- a/1toolConverter_local/tablas_extraidas.xlsx
+++ b/1toolConverter_local/tablas_extraidas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD228"/>
+  <dimension ref="A1:AD292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25454,6 +25454,6562 @@
       </c>
       <c r="AD228" t="inlineStr"/>
     </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Probe_1</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Probe 1</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>ANALOG_INPUT</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>60</v>
+      </c>
+      <c r="I229" t="n">
+        <v>3</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>-270</v>
+      </c>
+      <c r="L229" t="n">
+        <v>270</v>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>0</v>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z229" t="inlineStr"/>
+      <c r="AA229" t="inlineStr"/>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Probe_2</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Probe 2</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>ANALOG_INPUT</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>60</v>
+      </c>
+      <c r="I230" t="n">
+        <v>3</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>-270</v>
+      </c>
+      <c r="L230" t="n">
+        <v>270</v>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
+      <c r="AB230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Probe_3</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Probe 3</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ANALOG_INPUT</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>60</v>
+      </c>
+      <c r="I231" t="n">
+        <v>3</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>-270</v>
+      </c>
+      <c r="L231" t="n">
+        <v>270</v>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>0</v>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z231" t="inlineStr"/>
+      <c r="AA231" t="inlineStr"/>
+      <c r="AB231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Probe_4</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Probe 4</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>ANALOG_INPUT</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>60</v>
+      </c>
+      <c r="I232" t="n">
+        <v>3</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>-270</v>
+      </c>
+      <c r="L232" t="n">
+        <v>270</v>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z232" t="inlineStr"/>
+      <c r="AA232" t="inlineStr"/>
+      <c r="AB232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Regulation_probe</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Regulation probe</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>ANALOG_INPUT</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>60</v>
+      </c>
+      <c r="I233" t="n">
+        <v>3</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>-270</v>
+      </c>
+      <c r="L233" t="n">
+        <v>270</v>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>0</v>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z233" t="inlineStr"/>
+      <c r="AA233" t="inlineStr"/>
+      <c r="AB233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Real-time_speed_VSC1</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Real-time speed VSC1</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>ANALOG_INPUT</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>60</v>
+      </c>
+      <c r="I234" t="n">
+        <v>3</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>-270</v>
+      </c>
+      <c r="L234" t="n">
+        <v>270</v>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z234" t="inlineStr"/>
+      <c r="AA234" t="inlineStr"/>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>5639</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Real-time_speed_VSC2</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Real-time speed VSC2</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>ANALOG_INPUT</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>60</v>
+      </c>
+      <c r="I235" t="n">
+        <v>3</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>-270</v>
+      </c>
+      <c r="L235" t="n">
+        <v>270</v>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z235" t="inlineStr"/>
+      <c r="AA235" t="inlineStr"/>
+      <c r="AB235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SetPoint_VSC</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SetPoint VSC</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>SET_POINT</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>300</v>
+      </c>
+      <c r="I236" t="n">
+        <v>3</v>
+      </c>
+      <c r="J236" t="n">
+        <v>16</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z236" t="inlineStr"/>
+      <c r="AA236" t="inlineStr"/>
+      <c r="AB236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SetPoint_On/Off</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SetPoint On/Off</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>SET_POINT</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>300</v>
+      </c>
+      <c r="I237" t="n">
+        <v>3</v>
+      </c>
+      <c r="J237" t="n">
+        <v>16</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>0</v>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>16bit</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr"/>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z237" t="inlineStr"/>
+      <c r="AA237" t="inlineStr"/>
+      <c r="AB237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Digital_input_1_status</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Digital input 1 status</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>DIGITAL_INPUT</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>60</v>
+      </c>
+      <c r="I238" t="n">
+        <v>4</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>0</v>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr"/>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z238" t="inlineStr"/>
+      <c r="AA238" t="inlineStr"/>
+      <c r="AB238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Digital_input_2_status</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Digital input 2 status</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>DIGITAL_INPUT</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>60</v>
+      </c>
+      <c r="I239" t="n">
+        <v>4</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>0</v>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr"/>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z239" t="inlineStr"/>
+      <c r="AA239" t="inlineStr"/>
+      <c r="AB239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ONOFF_output_status</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ONOFF output status</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>60</v>
+      </c>
+      <c r="I240" t="n">
+        <v>4</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr"/>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z240" t="inlineStr"/>
+      <c r="AA240" t="inlineStr"/>
+      <c r="AB240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Defrost_1_output_status</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Defrost 1 output status</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>60</v>
+      </c>
+      <c r="I241" t="n">
+        <v>4</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>0</v>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr"/>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z241" t="inlineStr"/>
+      <c r="AA241" t="inlineStr"/>
+      <c r="AB241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Defrost_2_output_status</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Defrost 2 output status</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>60</v>
+      </c>
+      <c r="I242" t="n">
+        <v>4</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>0</v>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr"/>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z242" t="inlineStr"/>
+      <c r="AA242" t="inlineStr"/>
+      <c r="AB242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Alarm_output_status</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Alarm output status</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>60</v>
+      </c>
+      <c r="I243" t="n">
+        <v>4</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>0</v>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr"/>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z243" t="inlineStr"/>
+      <c r="AA243" t="inlineStr"/>
+      <c r="AB243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Light_output_status</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Light output status</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>60</v>
+      </c>
+      <c r="I244" t="n">
+        <v>1</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>1</v>
+      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>0</v>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr"/>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z244" t="inlineStr"/>
+      <c r="AA244" t="inlineStr"/>
+      <c r="AB244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Fan_output_status</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Fan output status</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>60</v>
+      </c>
+      <c r="I245" t="n">
+        <v>4</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>0</v>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr"/>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z245" t="inlineStr"/>
+      <c r="AA245" t="inlineStr"/>
+      <c r="AB245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Aux_output_status</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Aux output status</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>60</v>
+      </c>
+      <c r="I246" t="n">
+        <v>1</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>0</v>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr"/>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z246" t="inlineStr"/>
+      <c r="AA246" t="inlineStr"/>
+      <c r="AB246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Dead_band_output_status</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Dead band output status</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>60</v>
+      </c>
+      <c r="I247" t="n">
+        <v>4</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>0</v>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr"/>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z247" t="inlineStr"/>
+      <c r="AA247" t="inlineStr"/>
+      <c r="AB247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Compressor_1_output_status</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Compressor 1 output status</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>60</v>
+      </c>
+      <c r="I248" t="n">
+        <v>4</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" t="n">
+        <v>1</v>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>0</v>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr"/>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z248" t="inlineStr"/>
+      <c r="AA248" t="inlineStr"/>
+      <c r="AB248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Compressor_2_output_status</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Compressor 2 output status</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>60</v>
+      </c>
+      <c r="I249" t="n">
+        <v>4</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>0</v>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr"/>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z249" t="inlineStr"/>
+      <c r="AA249" t="inlineStr"/>
+      <c r="AB249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Buzzer_status</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Buzzer status</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>60</v>
+      </c>
+      <c r="I250" t="n">
+        <v>4</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>0</v>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr"/>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z250" t="inlineStr"/>
+      <c r="AA250" t="inlineStr"/>
+      <c r="AB250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Condenser_fan_output_status</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Condenser fan output status</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>60</v>
+      </c>
+      <c r="I251" t="n">
+        <v>4</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>0</v>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr"/>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y251" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z251" t="inlineStr"/>
+      <c r="AA251" t="inlineStr"/>
+      <c r="AB251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Heaters_output_status</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Heaters output status</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>DIGITAL_OUTPUT</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>60</v>
+      </c>
+      <c r="I252" t="n">
+        <v>4</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>1</v>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>0</v>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr"/>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z252" t="inlineStr"/>
+      <c r="AA252" t="inlineStr"/>
+      <c r="AB252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Device_ON</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Device ON</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>60</v>
+      </c>
+      <c r="I253" t="n">
+        <v>3</v>
+      </c>
+      <c r="J253" t="n">
+        <v>6</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>0</v>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr"/>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z253" t="inlineStr"/>
+      <c r="AA253" t="inlineStr"/>
+      <c r="AB253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Defrost_status</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Defrost status</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>60</v>
+      </c>
+      <c r="I254" t="n">
+        <v>3</v>
+      </c>
+      <c r="J254" t="n">
+        <v>6</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>1</v>
+      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>0</v>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr"/>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z254" t="inlineStr"/>
+      <c r="AA254" t="inlineStr"/>
+      <c r="AB254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Pull_down_status</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Pull down status</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>60</v>
+      </c>
+      <c r="I255" t="n">
+        <v>3</v>
+      </c>
+      <c r="J255" t="n">
+        <v>6</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>0</v>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr"/>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z255" t="inlineStr"/>
+      <c r="AA255" t="inlineStr"/>
+      <c r="AB255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Keyboard_lock/unlock</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Keyboard lock/unlock</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>60</v>
+      </c>
+      <c r="I256" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="n">
+        <v>1</v>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr"/>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z256" t="inlineStr"/>
+      <c r="AA256" t="inlineStr"/>
+      <c r="AB256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Alarm_muting</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Alarm muting</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>60</v>
+      </c>
+      <c r="I257" t="n">
+        <v>3</v>
+      </c>
+      <c r="J257" t="n">
+        <v>6</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>1</v>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>0</v>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr"/>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z257" t="inlineStr"/>
+      <c r="AA257" t="inlineStr"/>
+      <c r="AB257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Energy_saving_status</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Energy saving status</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>60</v>
+      </c>
+      <c r="I258" t="n">
+        <v>3</v>
+      </c>
+      <c r="J258" t="n">
+        <v>6</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>1</v>
+      </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>0</v>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr"/>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z258" t="inlineStr"/>
+      <c r="AA258" t="inlineStr"/>
+      <c r="AB258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Holiday_status</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Holiday status</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>60</v>
+      </c>
+      <c r="I259" t="n">
+        <v>3</v>
+      </c>
+      <c r="J259" t="n">
+        <v>6</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>1</v>
+      </c>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>0</v>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr"/>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z259" t="inlineStr"/>
+      <c r="AA259" t="inlineStr"/>
+      <c r="AB259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Test_mode_set_point_used</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Test mode set point used</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>basic</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>60</v>
+      </c>
+      <c r="I260" t="n">
+        <v>1</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="n">
+        <v>1</v>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>0</v>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr"/>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z260" t="inlineStr"/>
+      <c r="AA260" t="inlineStr"/>
+      <c r="AB260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Probe_1_error</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Probe 1 error</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>30</v>
+      </c>
+      <c r="I261" t="n">
+        <v>1</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="n">
+        <v>1</v>
+      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>0</v>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z261" t="inlineStr"/>
+      <c r="AA261" t="inlineStr"/>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Probe_2_error</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Probe 2 error</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>30</v>
+      </c>
+      <c r="I262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>0</v>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr"/>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z262" t="inlineStr"/>
+      <c r="AA262" t="inlineStr"/>
+      <c r="AB262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Probe_3_error</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Probe 3 error</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>30</v>
+      </c>
+      <c r="I263" t="n">
+        <v>1</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>0</v>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr"/>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z263" t="inlineStr"/>
+      <c r="AA263" t="inlineStr"/>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Probe_4_error</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Probe 4 error</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>30</v>
+      </c>
+      <c r="I264" t="n">
+        <v>1</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>1</v>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>0</v>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr"/>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z264" t="inlineStr"/>
+      <c r="AA264" t="inlineStr"/>
+      <c r="AB264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Hight_temperature_alarm</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Hight temperature alarm</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>30</v>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>1</v>
+      </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>0</v>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr"/>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z265" t="inlineStr"/>
+      <c r="AA265" t="inlineStr"/>
+      <c r="AB265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Low_temperature_alarm</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Low temperature alarm</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>30</v>
+      </c>
+      <c r="I266" t="n">
+        <v>1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>0</v>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr"/>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z266" t="inlineStr"/>
+      <c r="AA266" t="inlineStr"/>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Condenser_high_temperature_alarm</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Condenser high temperature alarm</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>30</v>
+      </c>
+      <c r="I267" t="n">
+        <v>1</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>0</v>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr"/>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z267" t="inlineStr"/>
+      <c r="AA267" t="inlineStr"/>
+      <c r="AB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Condenser_low_temperature_alarm</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Condenser low temperature alarm</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>30</v>
+      </c>
+      <c r="I268" t="n">
+        <v>1</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>0</v>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr"/>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z268" t="inlineStr"/>
+      <c r="AA268" t="inlineStr"/>
+      <c r="AB268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>External_warning_Alarm</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>External warning Alarm</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>30</v>
+      </c>
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1</v>
+      </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr"/>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z269" t="inlineStr"/>
+      <c r="AA269" t="inlineStr"/>
+      <c r="AB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Lock_alarm</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Lock alarm</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>30</v>
+      </c>
+      <c r="I270" t="n">
+        <v>1</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>1</v>
+      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr"/>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z270" t="inlineStr"/>
+      <c r="AA270" t="inlineStr"/>
+      <c r="AB270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Door_open_alarm</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Door open alarm</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>30</v>
+      </c>
+      <c r="I271" t="n">
+        <v>1</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr"/>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z271" t="inlineStr"/>
+      <c r="AA271" t="inlineStr"/>
+      <c r="AB271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>EEPROM_failure</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>EEPROM failure</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>30</v>
+      </c>
+      <c r="I272" t="n">
+        <v>1</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L272" t="n">
+        <v>1</v>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>0</v>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr"/>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z272" t="inlineStr"/>
+      <c r="AA272" t="inlineStr"/>
+      <c r="AB272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Pressure_switch_alarm</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Pressure switch alarm</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>30</v>
+      </c>
+      <c r="I273" t="n">
+        <v>1</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L273" t="n">
+        <v>1</v>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr"/>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z273" t="inlineStr"/>
+      <c r="AA273" t="inlineStr"/>
+      <c r="AB273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Real_time_clock_configuration_error</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Real time clock configuration error</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>30</v>
+      </c>
+      <c r="I274" t="n">
+        <v>1</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" t="n">
+        <v>1</v>
+      </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>0</v>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr"/>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y274" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z274" t="inlineStr"/>
+      <c r="AA274" t="inlineStr"/>
+      <c r="AB274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Embraco_compressor_Error</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Embraco compressor Error</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>30</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" t="n">
+        <v>1</v>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>0</v>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr"/>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y275" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z275" t="inlineStr"/>
+      <c r="AA275" t="inlineStr"/>
+      <c r="AB275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Secop_compressor_Error</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Secop compressor Error</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>30</v>
+      </c>
+      <c r="I276" t="n">
+        <v>1</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" t="n">
+        <v>1</v>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>0</v>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr"/>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z276" t="inlineStr"/>
+      <c r="AA276" t="inlineStr"/>
+      <c r="AB276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Compressor_1:_comunication_alarm</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Compressor 1: comunication alarm</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>30</v>
+      </c>
+      <c r="I277" t="n">
+        <v>1</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="n">
+        <v>1</v>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr"/>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z277" t="inlineStr"/>
+      <c r="AA277" t="inlineStr"/>
+      <c r="AB277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Compressor_2:_comunication_alarm</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Compressor 2: comunication alarm</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>ALARM</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>30</v>
+      </c>
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="n">
+        <v>1</v>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr"/>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>{"severity":"high"}</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z278" t="inlineStr"/>
+      <c r="AA278" t="inlineStr"/>
+      <c r="AB278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Device_ON_1</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Device ON</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>5</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr"/>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z279" t="inlineStr"/>
+      <c r="AA279" t="inlineStr"/>
+      <c r="AB279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Device_OFF</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Device OFF</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>5</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr"/>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z280" t="inlineStr"/>
+      <c r="AA280" t="inlineStr"/>
+      <c r="AB280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Defrost_ON</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Defrost ON</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>5</v>
+      </c>
+      <c r="K281" t="n">
+        <v>0</v>
+      </c>
+      <c r="L281" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr"/>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z281" t="inlineStr"/>
+      <c r="AA281" t="inlineStr"/>
+      <c r="AB281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Pull_Down_ON</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Pull Down ON</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
+        <v>5</v>
+      </c>
+      <c r="K282" t="n">
+        <v>0</v>
+      </c>
+      <c r="L282" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr"/>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y282" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z282" t="inlineStr"/>
+      <c r="AA282" t="inlineStr"/>
+      <c r="AB282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Pull_Down_OFF</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Pull Down OFF</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>5</v>
+      </c>
+      <c r="K283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L283" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr"/>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z283" t="inlineStr"/>
+      <c r="AA283" t="inlineStr"/>
+      <c r="AB283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Alarm_Muting_1</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Alarm Muting</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>5</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr"/>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y284" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z284" t="inlineStr"/>
+      <c r="AA284" t="inlineStr"/>
+      <c r="AB284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Energy_saving_ON</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Energy saving ON</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>5</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr"/>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z285" t="inlineStr"/>
+      <c r="AA285" t="inlineStr"/>
+      <c r="AB285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Energy_saving_OFF</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Energy saving OFF</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>5</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr"/>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z286" t="inlineStr"/>
+      <c r="AA286" t="inlineStr"/>
+      <c r="AB286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Light_ON</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Light ON</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>5</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L287" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr"/>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z287" t="inlineStr"/>
+      <c r="AA287" t="inlineStr"/>
+      <c r="AB287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Light_OFF</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Light OFF</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>5</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L288" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr"/>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z288" t="inlineStr"/>
+      <c r="AA288" t="inlineStr"/>
+      <c r="AB288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Aux_ON</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Aux ON</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>5</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr"/>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z289" t="inlineStr"/>
+      <c r="AA289" t="inlineStr"/>
+      <c r="AB289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Aux_OFF</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Aux OFF</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>5</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr"/>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z290" t="inlineStr"/>
+      <c r="AA290" t="inlineStr"/>
+      <c r="AB290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Holiday_ON</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Holiday ON</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>5</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr"/>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z291" t="inlineStr"/>
+      <c r="AA291" t="inlineStr"/>
+      <c r="AB291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Holiday_OFF</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Holiday OFF</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>COMMAND</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>5</v>
+      </c>
+      <c r="K292" t="n">
+        <v>0</v>
+      </c>
+      <c r="L292" t="n">
+        <v>9999</v>
+      </c>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>1bit</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr"/>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>{"severity":"none"}</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>{"_type":"l10n","default_lang":"en_US","translations":{"en_US":{"name":null,"_type":"languages","description":null}}}</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>modbus</t>
+        </is>
+      </c>
+      <c r="Y292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z292" t="inlineStr"/>
+      <c r="AA292" t="inlineStr"/>
+      <c r="AB292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD292" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
